--- a/survey/01_척도문항_총괄표_교수님검토용.xlsx
+++ b/survey/01_척도문항_총괄표_교수님검토용.xlsx
@@ -1277,7 +1277,6 @@
       <c r="F2" s="118" t="n"/>
       <c r="G2" s="119" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="106">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -1525,7 +1524,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="27" t="inlineStr">
         <is>
@@ -1543,7 +1541,6 @@
       <c r="F11" s="118" t="n"/>
       <c r="G11" s="119" t="n"/>
     </row>
-    <row r="12"/>
     <row r="13" ht="52.05" customHeight="1" s="106">
       <c r="A13" s="29" t="inlineStr">
         <is>
@@ -1619,7 +1616,6 @@
       <c r="F2" s="118" t="n"/>
       <c r="G2" s="119" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="106">
       <c r="A4" s="30" t="inlineStr">
         <is>
@@ -2188,7 +2184,6 @@
       </c>
       <c r="G20" s="40" t="n"/>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="109" t="inlineStr">
         <is>
@@ -2256,7 +2251,6 @@
       <c r="D2" s="118" t="n"/>
       <c r="E2" s="119" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="106">
       <c r="A4" s="42" t="inlineStr">
         <is>
@@ -2561,7 +2555,6 @@
       <c r="C2" s="118" t="n"/>
       <c r="D2" s="119" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="106">
       <c r="A4" s="51" t="inlineStr">
         <is>
@@ -2809,7 +2802,6 @@
       <c r="D2" s="118" t="n"/>
       <c r="E2" s="119" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="106">
       <c r="A4" s="117" t="inlineStr">
         <is>
@@ -2870,7 +2862,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="120" t="inlineStr">
         <is>
@@ -2999,7 +2990,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="120" t="inlineStr">
         <is>
@@ -3116,7 +3106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="7" customWidth="1" style="106" min="1" max="1"/>
@@ -3151,7 +3141,6 @@
       <c r="E2" s="118" t="n"/>
       <c r="F2" s="119" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="106">
       <c r="A4" s="74" t="inlineStr">
         <is>
@@ -3566,6 +3555,205 @@
       <c r="F16" s="90" t="inlineStr">
         <is>
           <t>Init. Change (4문항 중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>[2026-09-16 추가] 6차원 × 3문항으로 확대 — 차원당 2문항은 6요인 추정이 불안정하여 교수님 결정으로 문항 보강</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Q54</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Helping</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>나는 동료가 안전 절차를 잘 모를 때 알려 준다.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>정채점</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>본 연구 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Q55</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Voice</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>발언</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>나는 안전에 문제가 있다고 판단되면 상급자에게도 의견을 말한다.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>정채점</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>본 연구 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Q56</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Stewardship</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>자원참여</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>나는 요청받지 않아도 안전 점검이나 장비 관리에 손을 보탠다.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>정채점</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>본 연구 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Q57</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Whistleblowing</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>보고</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>나는 안전에 문제가 될 만한 상황을 덮지 않고 공식적으로 알린다.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>정채점</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>본 연구 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q58</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Civic Virtue</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>시민의식</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>나는 조직의 안전 방침이나 지침이 바뀌면 그 내용을 챙겨 본다.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>정채점</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>본 연구 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Q59</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Initiating Change</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>변화주도</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>나는 더 안전한 작업 방법을 찾아 제안한다.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>정채점</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>본 연구 추가</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="8" customWidth="1" style="106" min="1" max="1"/>
@@ -3606,7 +3794,6 @@
       <c r="D1" s="118" t="n"/>
       <c r="E1" s="119" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3" ht="30" customHeight="1" s="106">
       <c r="A3" s="91" t="inlineStr">
         <is>
@@ -4900,6 +5087,175 @@
         </is>
       </c>
       <c r="E50" s="89" t="inlineStr">
+        <is>
+          <t>정채점</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>[2026-09-16 추가 문항]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Q54</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>안전시민행동</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>나는 동료가 안전 절차를 잘 모를 때 알려 준다.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>정채점</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Q55</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>안전시민행동</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>발언</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>나는 안전에 문제가 있다고 판단되면 상급자에게도 의견을 말한다.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>정채점</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Q56</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>안전시민행동</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>자원참여</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>나는 요청받지 않아도 안전 점검이나 장비 관리에 손을 보탠다.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>정채점</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Q57</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>안전시민행동</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>보고</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>나는 안전에 문제가 될 만한 상황을 덮지 않고 공식적으로 알린다.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>정채점</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Q58</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>안전시민행동</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>시민의식</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>나는 조직의 안전 방침이나 지침이 바뀌면 그 내용을 챙겨 본다.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>정채점</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Q59</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>안전시민행동</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>변화주도</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>나는 더 안전한 작업 방법을 찾아 제안한다.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>정채점</t>
         </is>
@@ -4940,7 +5296,6 @@
       <c r="C1" s="118" t="n"/>
       <c r="D1" s="119" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3" ht="30" customHeight="1" s="106">
       <c r="A3" s="99" t="inlineStr">
         <is>
